--- a/time.xlsx
+++ b/time.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8400"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="time" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Metode FTCS</t>
   </si>
@@ -38,7 +38,13 @@
     <t>13m 1s +  3m 20s</t>
   </si>
   <si>
+    <t>13m 1s + 11m 35.2s + 9m 25.4 s</t>
+  </si>
+  <si>
     <t>18m 4.5 s + 3m 37.4 s</t>
+  </si>
+  <si>
+    <t>11m 21s + 12m 7.6s + 10m 25s + 12m 23.2 s</t>
   </si>
 </sst>
 </file>
@@ -1194,11 +1200,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:E5"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="4"/>
+  <dimension ref="B2:E4"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="12.7777777777778" customWidth="1"/>
     <col min="2" max="2" width="20.2222222222222" customWidth="1"/>
+    <col min="3" max="3" width="29.5555555555556" customWidth="1"/>
+    <col min="4" max="4" width="20.2222222222222" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5">
@@ -1229,10 +1237,14 @@
       <c r="B4" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="2:5">
-      <c r="B5" t="s">
+      <c r="C4" t="s">
         <v>3</v>
+      </c>
+      <c r="D4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
